--- a/test/testData/loginData.xlsx
+++ b/test/testData/loginData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94d7d777010aecee/Documents/WebDriverFramework/webdriverio-framework/test/testData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94d7d777010aecee/Documents/Vikash_Web/-PK-QA-WebdriverIO-Framework/test/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{5DACAB07-1D0B-4A5C-A4AC-A0B255B2795A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C66A18C6-6B92-4B58-B01C-2A4235418332}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{5DACAB07-1D0B-4A5C-A4AC-A0B255B2795A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC4848E8-CC9C-44C0-A494-CA9BB290D310}"/>
   <bookViews>
     <workbookView xWindow="2652" yWindow="2652" windowWidth="17280" windowHeight="8880" xr2:uid="{0ADA8EB8-2DF2-4A26-A2CE-340A80468ACF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>Piyush Kushwah</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>Email</t>
+  </si>
+  <si>
+    <t>piyushkushwah4022@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -109,6 +112,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -408,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19939B90-C72F-4E0C-8D15-2FE98DB494DF}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -430,9 +437,18 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{0E14426A-70AB-43A5-9339-7758FF9A7F26}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{26A535E6-56A7-4CEF-B342-794FB9B0A234}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
